--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3157,6 +3157,1461 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120315940</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>283499</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6527964</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120315960</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>283506</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6528143</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120315991</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>283523</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6528173</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120315969</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105564</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>283509</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6528148</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120315947</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>283569</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6527994</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120315929</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>283496</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6527938</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120315949</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>283557</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6528002</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120315972</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100171</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>283509</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6528148</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120315927</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57463</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>283528</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6528020</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120315912</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>283535</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6528012</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120315982</v>
+      </c>
+      <c r="B32" t="n">
+        <v>105564</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>283523</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6528173</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120315942</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>283569</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6527965</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120315953</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Överby-Holma, Boh</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>283450</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6527951</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4612,6 +4612,911 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120319318</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Skee, Boh</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>283678</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6528180</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hackspår i en gammal halvdöd tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120325399</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>283598</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6527990</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Massor av hack en gammal nyss död gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120325558</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>283571</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6528000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120319417</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>283722</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6528065</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120325465</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>283549</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6528013</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Kanske flera många hack på en död tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120325002</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>283612</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6528016</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120324201</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>283761</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6528094</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd gammal gran</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315940</v>
+        <v>120315982</v>
       </c>
       <c r="B22" t="n">
-        <v>57326</v>
+        <v>105588</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,35 +3171,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3207,10 +3203,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283499</v>
+        <v>283523</v>
       </c>
       <c r="R22" t="n">
-        <v>6527964</v>
+        <v>6528173</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3245,12 +3241,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3269,10 +3271,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315960</v>
+        <v>120315947</v>
       </c>
       <c r="B23" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3281,35 +3283,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3317,10 +3319,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283506</v>
+        <v>283569</v>
       </c>
       <c r="R23" t="n">
-        <v>6528143</v>
+        <v>6527994</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3361,6 +3363,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3379,10 +3382,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315991</v>
+        <v>120315960</v>
       </c>
       <c r="B24" t="n">
-        <v>100171</v>
+        <v>57336</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3391,31 +3394,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3423,10 +3430,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283523</v>
+        <v>283506</v>
       </c>
       <c r="R24" t="n">
-        <v>6528173</v>
+        <v>6528143</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3461,18 +3468,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mängder, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3494,7 +3495,7 @@
         <v>120315969</v>
       </c>
       <c r="B25" t="n">
-        <v>105564</v>
+        <v>105588</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3603,10 +3604,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315947</v>
+        <v>120315953</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3615,35 +3616,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3651,10 +3652,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283569</v>
+        <v>283450</v>
       </c>
       <c r="R26" t="n">
-        <v>6527994</v>
+        <v>6527951</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3695,7 +3696,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315929</v>
+        <v>120315942</v>
       </c>
       <c r="B27" t="n">
-        <v>57326</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,35 +3726,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283496</v>
+        <v>283569</v>
       </c>
       <c r="R27" t="n">
-        <v>6527938</v>
+        <v>6527965</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3806,6 +3806,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3824,10 +3825,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315949</v>
+        <v>120315927</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3836,35 +3837,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3872,10 +3877,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283557</v>
+        <v>283528</v>
       </c>
       <c r="R28" t="n">
-        <v>6528002</v>
+        <v>6528020</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3910,13 +3915,17 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3938,7 +3947,7 @@
         <v>120315972</v>
       </c>
       <c r="B29" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4047,10 +4056,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315927</v>
+        <v>120315929</v>
       </c>
       <c r="B30" t="n">
-        <v>57463</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4063,33 +4072,29 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4099,10 +4104,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283528</v>
+        <v>283496</v>
       </c>
       <c r="R30" t="n">
-        <v>6528020</v>
+        <v>6527938</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4135,11 +4140,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4169,7 +4169,7 @@
         <v>120315912</v>
       </c>
       <c r="B31" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315982</v>
+        <v>120315940</v>
       </c>
       <c r="B32" t="n">
-        <v>105564</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4293,31 +4293,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4325,10 +4329,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283523</v>
+        <v>283499</v>
       </c>
       <c r="R32" t="n">
-        <v>6528173</v>
+        <v>6527964</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4363,18 +4367,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4393,10 +4391,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315942</v>
+        <v>120315949</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4428,7 +4426,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4441,10 +4439,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283569</v>
+        <v>283557</v>
       </c>
       <c r="R33" t="n">
-        <v>6527965</v>
+        <v>6528002</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4504,10 +4502,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315953</v>
+        <v>120315991</v>
       </c>
       <c r="B34" t="n">
-        <v>57326</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4516,35 +4514,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4552,10 +4546,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283450</v>
+        <v>283523</v>
       </c>
       <c r="R34" t="n">
-        <v>6527951</v>
+        <v>6528173</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4590,12 +4584,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120319318</v>
+        <v>120325002</v>
       </c>
       <c r="B35" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4654,18 +4654,22 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283678</v>
+        <v>283612</v>
       </c>
       <c r="R35" t="n">
-        <v>6528180</v>
+        <v>6528016</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4697,7 +4701,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4707,12 +4711,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4744,7 +4743,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120325399</v>
+        <v>120319318</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4788,14 +4787,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283598</v>
+        <v>283678</v>
       </c>
       <c r="R36" t="n">
-        <v>6527990</v>
+        <v>6528180</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4827,7 +4826,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4837,12 +4836,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4874,10 +4873,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120325558</v>
+        <v>120319417</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4886,35 +4885,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4922,10 +4921,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283571</v>
+        <v>283722</v>
       </c>
       <c r="R37" t="n">
-        <v>6528000</v>
+        <v>6528065</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4957,7 +4956,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4967,7 +4966,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4976,7 +4980,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5000,10 +5003,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120319417</v>
+        <v>120325465</v>
       </c>
       <c r="B38" t="n">
-        <v>57326</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5048,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283722</v>
+        <v>283549</v>
       </c>
       <c r="R38" t="n">
-        <v>6528065</v>
+        <v>6528013</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5083,7 +5086,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5093,12 +5096,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5130,7 +5133,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120325465</v>
+        <v>120324201</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5178,10 +5181,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283549</v>
+        <v>283761</v>
       </c>
       <c r="R39" t="n">
-        <v>6528013</v>
+        <v>6528094</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5213,7 +5216,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5223,12 +5226,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kanske flera många hack på en död tall</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5260,7 +5263,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120325002</v>
+        <v>120325399</v>
       </c>
       <c r="B40" t="n">
         <v>57336</v>
@@ -5300,11 +5303,7 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5312,10 +5311,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283612</v>
+        <v>283598</v>
       </c>
       <c r="R40" t="n">
-        <v>6528016</v>
+        <v>6527990</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5358,6 +5357,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5389,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120324201</v>
+        <v>120325558</v>
       </c>
       <c r="B41" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5401,35 +5405,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5437,10 +5441,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283761</v>
+        <v>283571</v>
       </c>
       <c r="R41" t="n">
-        <v>6528094</v>
+        <v>6528000</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5472,7 +5476,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5482,12 +5486,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5496,6 +5495,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -4166,10 +4166,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315912</v>
+        <v>120315940</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,16 +4182,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283535</v>
+        <v>283499</v>
       </c>
       <c r="R31" t="n">
-        <v>6528012</v>
+        <v>6527964</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4250,11 +4250,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4281,10 +4276,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315940</v>
+        <v>120315912</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4297,16 +4292,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4329,10 +4324,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283499</v>
+        <v>283535</v>
       </c>
       <c r="R32" t="n">
-        <v>6527964</v>
+        <v>6528012</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4365,6 +4360,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315982</v>
+        <v>120315940</v>
       </c>
       <c r="B22" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,31 +3171,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3203,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283523</v>
+        <v>283499</v>
       </c>
       <c r="R22" t="n">
-        <v>6528173</v>
+        <v>6527964</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3241,18 +3245,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3271,10 +3269,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315947</v>
+        <v>120315929</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3283,35 +3281,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3319,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283569</v>
+        <v>283496</v>
       </c>
       <c r="R23" t="n">
-        <v>6527994</v>
+        <v>6527938</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3363,7 +3361,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3382,10 +3379,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315960</v>
+        <v>120315912</v>
       </c>
       <c r="B24" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3398,16 +3395,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3420,7 +3417,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3430,10 +3427,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283506</v>
+        <v>283535</v>
       </c>
       <c r="R24" t="n">
-        <v>6528143</v>
+        <v>6528012</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3466,6 +3463,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3492,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315969</v>
+        <v>120315942</v>
       </c>
       <c r="B25" t="n">
-        <v>105588</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3504,28 +3506,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -3536,10 +3542,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283509</v>
+        <v>283569</v>
       </c>
       <c r="R25" t="n">
-        <v>6528148</v>
+        <v>6527965</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3572,11 +3578,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3604,7 +3605,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315953</v>
+        <v>120315960</v>
       </c>
       <c r="B26" t="n">
         <v>57336</v>
@@ -3642,7 +3643,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3652,10 +3653,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283450</v>
+        <v>283506</v>
       </c>
       <c r="R26" t="n">
-        <v>6527951</v>
+        <v>6528143</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3714,10 +3715,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315942</v>
+        <v>120315953</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3726,35 +3727,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3763,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283569</v>
+        <v>283450</v>
       </c>
       <c r="R27" t="n">
-        <v>6527965</v>
+        <v>6527951</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3806,7 +3807,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3825,10 +3825,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315927</v>
+        <v>120315982</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>105588</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3837,39 +3837,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3877,10 +3869,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283528</v>
+        <v>283523</v>
       </c>
       <c r="R28" t="n">
-        <v>6528020</v>
+        <v>6528173</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3917,7 +3909,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett par i sitt permanenta revir</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3926,6 +3918,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3944,10 +3937,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315972</v>
+        <v>120315969</v>
       </c>
       <c r="B29" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3956,25 +3949,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4028,7 +4021,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4056,10 +4049,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315929</v>
+        <v>120315947</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4068,35 +4061,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4104,10 +4097,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283496</v>
+        <v>283569</v>
       </c>
       <c r="R30" t="n">
-        <v>6527938</v>
+        <v>6527994</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4148,6 +4141,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4166,10 +4160,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315940</v>
+        <v>120315991</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4178,35 +4172,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4214,10 +4204,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283499</v>
+        <v>283523</v>
       </c>
       <c r="R31" t="n">
-        <v>6527964</v>
+        <v>6528173</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4252,12 +4242,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4276,10 +4272,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315912</v>
+        <v>120315972</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>100194</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4288,35 +4284,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4324,10 +4316,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283535</v>
+        <v>283509</v>
       </c>
       <c r="R32" t="n">
-        <v>6528012</v>
+        <v>6528148</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4364,7 +4356,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Färska hackringar/spår på flera träd</t>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4373,6 +4365,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4502,10 +4495,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315991</v>
+        <v>120315927</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4514,31 +4507,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4546,10 +4547,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283523</v>
+        <v>283528</v>
       </c>
       <c r="R34" t="n">
-        <v>6528173</v>
+        <v>6528020</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4586,7 +4587,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mängder, kalkinslag i marken</t>
+          <t>Ett par i sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4595,7 +4596,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120325002</v>
+        <v>120325465</v>
       </c>
       <c r="B35" t="n">
         <v>57336</v>
@@ -4654,11 +4654,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4666,10 +4662,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283612</v>
+        <v>283549</v>
       </c>
       <c r="R35" t="n">
-        <v>6528016</v>
+        <v>6528013</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4701,7 +4697,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4711,7 +4707,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4743,7 +4744,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120319318</v>
+        <v>120325399</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4787,14 +4788,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283678</v>
+        <v>283598</v>
       </c>
       <c r="R36" t="n">
-        <v>6528180</v>
+        <v>6527990</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4826,7 +4827,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4836,12 +4837,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4873,7 +4874,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120319417</v>
+        <v>120325002</v>
       </c>
       <c r="B37" t="n">
         <v>57336</v>
@@ -4913,7 +4914,11 @@
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4921,10 +4926,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283722</v>
+        <v>283612</v>
       </c>
       <c r="R37" t="n">
-        <v>6528065</v>
+        <v>6528016</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4956,7 +4961,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4966,12 +4971,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5003,10 +5003,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120325465</v>
+        <v>120325558</v>
       </c>
       <c r="B38" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5015,35 +5015,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283549</v>
+        <v>283571</v>
       </c>
       <c r="R38" t="n">
-        <v>6528013</v>
+        <v>6528000</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5099,17 +5099,13 @@
           <t>15:30</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Kanske flera många hack på en död tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5133,7 +5129,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120324201</v>
+        <v>120319417</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5181,10 +5177,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283761</v>
+        <v>283722</v>
       </c>
       <c r="R39" t="n">
-        <v>6528094</v>
+        <v>6528065</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5231,7 +5227,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5263,7 +5259,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120325399</v>
+        <v>120324201</v>
       </c>
       <c r="B40" t="n">
         <v>57336</v>
@@ -5311,10 +5307,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283598</v>
+        <v>283761</v>
       </c>
       <c r="R40" t="n">
-        <v>6527990</v>
+        <v>6528094</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5346,7 +5342,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5356,12 +5352,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5393,10 +5389,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120325558</v>
+        <v>120319318</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5405,46 +5401,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283571</v>
+        <v>283678</v>
       </c>
       <c r="R41" t="n">
-        <v>6528000</v>
+        <v>6528180</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5476,7 +5472,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5486,7 +5482,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5495,7 +5496,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315940</v>
+        <v>120315991</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,35 +3171,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3207,10 +3203,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283499</v>
+        <v>283523</v>
       </c>
       <c r="R22" t="n">
-        <v>6527964</v>
+        <v>6528173</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3245,12 +3241,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3269,10 +3271,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315929</v>
+        <v>120315969</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3281,35 +3283,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3317,10 +3315,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283496</v>
+        <v>283509</v>
       </c>
       <c r="R23" t="n">
-        <v>6527938</v>
+        <v>6528148</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3355,12 +3353,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3379,10 +3383,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315912</v>
+        <v>120315949</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3391,35 +3395,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3427,10 +3431,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283535</v>
+        <v>283557</v>
       </c>
       <c r="R24" t="n">
-        <v>6528012</v>
+        <v>6528002</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3465,17 +3469,13 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska hackringar/spår på flera träd</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3494,10 +3494,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315942</v>
+        <v>120315972</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3506,32 +3506,28 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -3542,10 +3538,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283569</v>
+        <v>283509</v>
       </c>
       <c r="R25" t="n">
-        <v>6527965</v>
+        <v>6528148</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3578,6 +3574,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3605,10 +3606,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315960</v>
+        <v>120315912</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3621,16 +3622,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3643,7 +3644,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3653,10 +3654,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283506</v>
+        <v>283535</v>
       </c>
       <c r="R26" t="n">
-        <v>6528143</v>
+        <v>6528012</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3689,6 +3690,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3715,7 +3721,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315953</v>
+        <v>120315940</v>
       </c>
       <c r="B27" t="n">
         <v>57336</v>
@@ -3763,10 +3769,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283450</v>
+        <v>283499</v>
       </c>
       <c r="R27" t="n">
-        <v>6527951</v>
+        <v>6527964</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3825,10 +3831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315982</v>
+        <v>120315960</v>
       </c>
       <c r="B28" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3837,31 +3843,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3869,10 +3879,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283523</v>
+        <v>283506</v>
       </c>
       <c r="R28" t="n">
-        <v>6528173</v>
+        <v>6528143</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3907,18 +3917,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3937,7 +3941,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315969</v>
+        <v>120315982</v>
       </c>
       <c r="B29" t="n">
         <v>105588</v>
@@ -3981,10 +3985,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>283509</v>
+        <v>283523</v>
       </c>
       <c r="R29" t="n">
-        <v>6528148</v>
+        <v>6528173</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4160,10 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315991</v>
+        <v>120315929</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4172,31 +4176,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4204,10 +4212,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283523</v>
+        <v>283496</v>
       </c>
       <c r="R31" t="n">
-        <v>6528173</v>
+        <v>6527938</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4242,18 +4250,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mängder, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4272,10 +4274,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315972</v>
+        <v>120315953</v>
       </c>
       <c r="B32" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4284,31 +4286,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4316,10 +4322,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283509</v>
+        <v>283450</v>
       </c>
       <c r="R32" t="n">
-        <v>6528148</v>
+        <v>6527951</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4354,18 +4360,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4384,7 +4384,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315949</v>
+        <v>120315942</v>
       </c>
       <c r="B33" t="n">
         <v>97930</v>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283557</v>
+        <v>283569</v>
       </c>
       <c r="R33" t="n">
-        <v>6528002</v>
+        <v>6527965</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120325465</v>
+        <v>120325002</v>
       </c>
       <c r="B35" t="n">
         <v>57336</v>
@@ -4654,7 +4654,11 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4662,10 +4666,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283549</v>
+        <v>283612</v>
       </c>
       <c r="R35" t="n">
-        <v>6528013</v>
+        <v>6528016</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4697,7 +4701,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4707,12 +4711,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Kanske flera många hack på en död tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4744,7 +4743,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120325399</v>
+        <v>120319318</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4788,14 +4787,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283598</v>
+        <v>283678</v>
       </c>
       <c r="R36" t="n">
-        <v>6527990</v>
+        <v>6528180</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4827,7 +4826,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4837,12 +4836,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4874,10 +4873,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120325002</v>
+        <v>120325558</v>
       </c>
       <c r="B37" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4886,39 +4885,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4926,10 +4921,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283612</v>
+        <v>283571</v>
       </c>
       <c r="R37" t="n">
-        <v>6528016</v>
+        <v>6528000</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4961,7 +4956,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4971,7 +4966,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,6 +4975,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5003,10 +4999,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120325558</v>
+        <v>120325399</v>
       </c>
       <c r="B38" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5015,35 +5011,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5051,10 +5047,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283571</v>
+        <v>283598</v>
       </c>
       <c r="R38" t="n">
-        <v>6528000</v>
+        <v>6527990</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5086,7 +5082,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5096,7 +5092,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5105,7 +5106,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5129,7 +5129,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120319417</v>
+        <v>120325465</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283722</v>
+        <v>283549</v>
       </c>
       <c r="R39" t="n">
-        <v>6528065</v>
+        <v>6528013</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5259,7 +5259,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120324201</v>
+        <v>120319417</v>
       </c>
       <c r="B40" t="n">
         <v>57336</v>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283761</v>
+        <v>283722</v>
       </c>
       <c r="R40" t="n">
-        <v>6528094</v>
+        <v>6528065</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5389,7 +5389,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120319318</v>
+        <v>120324201</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5433,14 +5433,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283678</v>
+        <v>283761</v>
       </c>
       <c r="R41" t="n">
-        <v>6528180</v>
+        <v>6528094</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -4053,10 +4053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315947</v>
+        <v>120315929</v>
       </c>
       <c r="B30" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4065,35 +4065,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283569</v>
+        <v>283496</v>
       </c>
       <c r="R30" t="n">
-        <v>6527994</v>
+        <v>6527938</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4145,7 +4145,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4164,10 +4163,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315929</v>
+        <v>120315947</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4176,35 +4175,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4212,10 +4211,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283496</v>
+        <v>283569</v>
       </c>
       <c r="R31" t="n">
-        <v>6527938</v>
+        <v>6527994</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4256,6 +4255,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4384,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315942</v>
+        <v>120315927</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4396,35 +4396,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4432,10 +4436,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283569</v>
+        <v>283528</v>
       </c>
       <c r="R33" t="n">
-        <v>6527965</v>
+        <v>6528020</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4470,13 +4474,17 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4495,10 +4503,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315927</v>
+        <v>120315942</v>
       </c>
       <c r="B34" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4507,39 +4515,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4547,10 +4551,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283528</v>
+        <v>283569</v>
       </c>
       <c r="R34" t="n">
-        <v>6528020</v>
+        <v>6527965</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4585,17 +4589,13 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315991</v>
+        <v>120315927</v>
       </c>
       <c r="B22" t="n">
-        <v>100194</v>
+        <v>57473</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,31 +3171,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3203,10 +3211,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283523</v>
+        <v>283528</v>
       </c>
       <c r="R22" t="n">
-        <v>6528173</v>
+        <v>6528020</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3243,7 +3251,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Mängder, kalkinslag i marken</t>
+          <t>Ett par i sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3252,7 +3260,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3271,10 +3278,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315969</v>
+        <v>120315953</v>
       </c>
       <c r="B23" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3283,31 +3290,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3315,10 +3326,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283509</v>
+        <v>283450</v>
       </c>
       <c r="R23" t="n">
-        <v>6528148</v>
+        <v>6527951</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3353,18 +3364,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3383,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315949</v>
+        <v>120315972</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3395,32 +3400,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -3431,10 +3432,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283557</v>
+        <v>283509</v>
       </c>
       <c r="R24" t="n">
-        <v>6528002</v>
+        <v>6528148</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3467,6 +3468,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3494,10 +3500,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315972</v>
+        <v>120315960</v>
       </c>
       <c r="B25" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3506,31 +3512,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3538,10 +3548,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283509</v>
+        <v>283506</v>
       </c>
       <c r="R25" t="n">
-        <v>6528148</v>
+        <v>6528143</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3576,18 +3586,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3606,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315912</v>
+        <v>120315929</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>57336</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,16 +3626,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3654,10 +3658,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283535</v>
+        <v>283496</v>
       </c>
       <c r="R26" t="n">
-        <v>6528012</v>
+        <v>6527938</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3690,11 +3694,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3721,10 +3720,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315940</v>
+        <v>120315912</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3737,16 +3736,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3769,10 +3768,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283499</v>
+        <v>283535</v>
       </c>
       <c r="R27" t="n">
-        <v>6527964</v>
+        <v>6528012</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3805,6 +3804,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3831,10 +3835,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315960</v>
+        <v>120315969</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,35 +3847,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283506</v>
+        <v>283509</v>
       </c>
       <c r="R28" t="n">
-        <v>6528143</v>
+        <v>6528148</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3917,12 +3917,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3941,10 +3947,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315982</v>
+        <v>120315947</v>
       </c>
       <c r="B29" t="n">
-        <v>105588</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3953,28 +3959,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -3985,10 +3995,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>283523</v>
+        <v>283569</v>
       </c>
       <c r="R29" t="n">
-        <v>6528173</v>
+        <v>6527994</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4021,11 +4031,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4053,10 +4058,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315929</v>
+        <v>120315982</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4065,35 +4070,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4101,10 +4102,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283496</v>
+        <v>283523</v>
       </c>
       <c r="R30" t="n">
-        <v>6527938</v>
+        <v>6528173</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4139,12 +4140,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4163,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315947</v>
+        <v>120315991</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4175,32 +4182,28 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -4211,10 +4214,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283569</v>
+        <v>283523</v>
       </c>
       <c r="R31" t="n">
-        <v>6527994</v>
+        <v>6528173</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4247,6 +4250,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4274,10 +4282,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315953</v>
+        <v>120315949</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4286,35 +4294,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4322,10 +4330,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283450</v>
+        <v>283557</v>
       </c>
       <c r="R32" t="n">
-        <v>6527951</v>
+        <v>6528002</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4366,6 +4374,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4384,10 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315927</v>
+        <v>120315942</v>
       </c>
       <c r="B33" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4396,39 +4405,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283528</v>
+        <v>283569</v>
       </c>
       <c r="R33" t="n">
-        <v>6528020</v>
+        <v>6527965</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4474,17 +4479,13 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4503,10 +4504,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315942</v>
+        <v>120315940</v>
       </c>
       <c r="B34" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4515,35 +4516,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4551,10 +4552,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283569</v>
+        <v>283499</v>
       </c>
       <c r="R34" t="n">
-        <v>6527965</v>
+        <v>6527964</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4595,7 +4596,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120325002</v>
+        <v>120324201</v>
       </c>
       <c r="B35" t="n">
         <v>57336</v>
@@ -4654,11 +4654,7 @@
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4666,10 +4662,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283612</v>
+        <v>283761</v>
       </c>
       <c r="R35" t="n">
-        <v>6528016</v>
+        <v>6528094</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4701,7 +4697,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4711,7 +4707,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4743,7 +4744,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120319318</v>
+        <v>120325002</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4783,18 +4784,22 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283678</v>
+        <v>283612</v>
       </c>
       <c r="R36" t="n">
-        <v>6528180</v>
+        <v>6528016</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4826,7 +4831,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4836,12 +4841,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120325558</v>
+        <v>120319417</v>
       </c>
       <c r="B37" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4885,35 +4885,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283571</v>
+        <v>283722</v>
       </c>
       <c r="R37" t="n">
-        <v>6528000</v>
+        <v>6528065</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4966,7 +4966,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4975,7 +4980,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4999,7 +5003,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120325399</v>
+        <v>120325465</v>
       </c>
       <c r="B38" t="n">
         <v>57336</v>
@@ -5047,10 +5051,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283598</v>
+        <v>283549</v>
       </c>
       <c r="R38" t="n">
-        <v>6527990</v>
+        <v>6528013</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5082,7 +5086,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5092,12 +5096,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5129,7 +5133,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120325465</v>
+        <v>120325399</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5177,10 +5181,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283549</v>
+        <v>283598</v>
       </c>
       <c r="R39" t="n">
-        <v>6528013</v>
+        <v>6527990</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5212,7 +5216,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5222,12 +5226,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Kanske flera många hack på en död tall</t>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5259,10 +5263,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120319417</v>
+        <v>120325558</v>
       </c>
       <c r="B40" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5271,35 +5275,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5307,10 +5311,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283722</v>
+        <v>283571</v>
       </c>
       <c r="R40" t="n">
-        <v>6528065</v>
+        <v>6528000</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5342,7 +5346,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5352,12 +5356,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5366,6 +5365,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5389,7 +5389,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120324201</v>
+        <v>120319318</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5433,14 +5433,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283761</v>
+        <v>283678</v>
       </c>
       <c r="R41" t="n">
-        <v>6528094</v>
+        <v>6528180</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315927</v>
+        <v>120315982</v>
       </c>
       <c r="B22" t="n">
-        <v>57473</v>
+        <v>105588</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,39 +3171,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3211,10 +3203,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283528</v>
+        <v>283523</v>
       </c>
       <c r="R22" t="n">
-        <v>6528020</v>
+        <v>6528173</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3251,7 +3243,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ett par i sitt permanenta revir</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3260,6 +3252,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3278,7 +3271,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315953</v>
+        <v>120315940</v>
       </c>
       <c r="B23" t="n">
         <v>57336</v>
@@ -3326,10 +3319,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283450</v>
+        <v>283499</v>
       </c>
       <c r="R23" t="n">
-        <v>6527951</v>
+        <v>6527964</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3388,10 +3381,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315972</v>
+        <v>120315949</v>
       </c>
       <c r="B24" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3400,28 +3393,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -3432,10 +3429,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283509</v>
+        <v>283557</v>
       </c>
       <c r="R24" t="n">
-        <v>6528148</v>
+        <v>6528002</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3468,11 +3465,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3500,10 +3492,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315960</v>
+        <v>120315912</v>
       </c>
       <c r="B25" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3516,16 +3508,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3538,7 +3530,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3548,10 +3540,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283506</v>
+        <v>283535</v>
       </c>
       <c r="R25" t="n">
-        <v>6528143</v>
+        <v>6528012</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3584,6 +3576,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3610,10 +3607,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315929</v>
+        <v>120315991</v>
       </c>
       <c r="B26" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3622,35 +3619,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3658,10 +3651,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283496</v>
+        <v>283523</v>
       </c>
       <c r="R26" t="n">
-        <v>6527938</v>
+        <v>6528173</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3696,12 +3689,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3720,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315912</v>
+        <v>120315969</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>105588</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3732,35 +3731,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220785</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3768,10 +3763,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283535</v>
+        <v>283509</v>
       </c>
       <c r="R27" t="n">
-        <v>6528012</v>
+        <v>6528148</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska hackringar/spår på flera träd</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3817,6 +3812,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3835,10 +3831,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315969</v>
+        <v>120315929</v>
       </c>
       <c r="B28" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3847,31 +3843,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283509</v>
+        <v>283496</v>
       </c>
       <c r="R28" t="n">
-        <v>6528148</v>
+        <v>6527938</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3917,18 +3917,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3947,7 +3941,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315947</v>
+        <v>120315942</v>
       </c>
       <c r="B29" t="n">
         <v>97930</v>
@@ -3998,7 +3992,7 @@
         <v>283569</v>
       </c>
       <c r="R29" t="n">
-        <v>6527994</v>
+        <v>6527965</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4058,10 +4052,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315982</v>
+        <v>120315953</v>
       </c>
       <c r="B30" t="n">
-        <v>105588</v>
+        <v>57336</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4070,31 +4064,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4102,10 +4100,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283523</v>
+        <v>283450</v>
       </c>
       <c r="R30" t="n">
-        <v>6528173</v>
+        <v>6527951</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4140,18 +4138,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4170,10 +4162,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315991</v>
+        <v>120315947</v>
       </c>
       <c r="B31" t="n">
-        <v>100194</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4182,28 +4174,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -4214,10 +4210,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283523</v>
+        <v>283569</v>
       </c>
       <c r="R31" t="n">
-        <v>6528173</v>
+        <v>6527994</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4250,11 +4246,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mängder, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4282,10 +4273,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315949</v>
+        <v>120315927</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4294,35 +4285,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4330,10 +4325,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283557</v>
+        <v>283528</v>
       </c>
       <c r="R32" t="n">
-        <v>6528002</v>
+        <v>6528020</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4368,13 +4363,17 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4393,10 +4392,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315942</v>
+        <v>120315960</v>
       </c>
       <c r="B33" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4405,35 +4404,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4441,10 +4440,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283569</v>
+        <v>283506</v>
       </c>
       <c r="R33" t="n">
-        <v>6527965</v>
+        <v>6528143</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4485,7 +4484,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4504,10 +4502,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315940</v>
+        <v>120315972</v>
       </c>
       <c r="B34" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4516,35 +4514,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4552,10 +4546,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283499</v>
+        <v>283509</v>
       </c>
       <c r="R34" t="n">
-        <v>6527964</v>
+        <v>6528148</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4590,12 +4584,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4614,7 +4614,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120324201</v>
+        <v>120325399</v>
       </c>
       <c r="B35" t="n">
         <v>57336</v>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283761</v>
+        <v>283598</v>
       </c>
       <c r="R35" t="n">
-        <v>6528094</v>
+        <v>6527990</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4744,7 +4744,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120325002</v>
+        <v>120319417</v>
       </c>
       <c r="B36" t="n">
         <v>57336</v>
@@ -4784,11 +4784,7 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4796,10 +4792,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283612</v>
+        <v>283722</v>
       </c>
       <c r="R36" t="n">
-        <v>6528016</v>
+        <v>6528065</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4831,7 +4827,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4841,7 +4837,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4873,7 +4874,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120319417</v>
+        <v>120325465</v>
       </c>
       <c r="B37" t="n">
         <v>57336</v>
@@ -4921,10 +4922,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283722</v>
+        <v>283549</v>
       </c>
       <c r="R37" t="n">
-        <v>6528065</v>
+        <v>6528013</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4956,7 +4957,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4966,12 +4967,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5003,7 +5004,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120325465</v>
+        <v>120319318</v>
       </c>
       <c r="B38" t="n">
         <v>57336</v>
@@ -5047,14 +5048,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283549</v>
+        <v>283678</v>
       </c>
       <c r="R38" t="n">
-        <v>6528013</v>
+        <v>6528180</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5086,7 +5087,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5096,12 +5097,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Kanske flera många hack på en död tall</t>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5133,7 +5134,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120325399</v>
+        <v>120324201</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5181,10 +5182,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283598</v>
+        <v>283761</v>
       </c>
       <c r="R39" t="n">
-        <v>6527990</v>
+        <v>6528094</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5216,7 +5217,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5226,12 +5227,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5389,7 +5390,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120319318</v>
+        <v>120325002</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5429,18 +5430,22 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283678</v>
+        <v>283612</v>
       </c>
       <c r="R41" t="n">
-        <v>6528180</v>
+        <v>6528016</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5472,7 +5477,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5482,12 +5487,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3607,10 +3607,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315991</v>
+        <v>120315969</v>
       </c>
       <c r="B26" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283523</v>
+        <v>283509</v>
       </c>
       <c r="R26" t="n">
-        <v>6528173</v>
+        <v>6528148</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Mängder, kalkinslag i marken</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315969</v>
+        <v>120315991</v>
       </c>
       <c r="B27" t="n">
-        <v>105588</v>
+        <v>100194</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3763,10 +3763,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283509</v>
+        <v>283523</v>
       </c>
       <c r="R27" t="n">
-        <v>6528148</v>
+        <v>6528173</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Mängder med små askar</t>
+          <t>Mängder, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5517,6 +5517,625 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120512850</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>283234</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6527956</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120512348</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>283306</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6528054</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hack i en döende tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120513970</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57689</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>283036</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6527980</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Endast hörde</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120514783</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>283211</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6528028</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hack på döende stor björk</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120514265</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56532</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>283173</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6528043</v>
+      </c>
+      <c r="S46" t="n">
+        <v>50</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315982</v>
+        <v>120315947</v>
       </c>
       <c r="B22" t="n">
-        <v>105588</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,28 +3171,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -3203,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283523</v>
+        <v>283569</v>
       </c>
       <c r="R22" t="n">
-        <v>6528173</v>
+        <v>6527994</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3239,11 +3243,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3271,10 +3270,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315940</v>
+        <v>120315942</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3283,35 +3282,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3319,10 +3318,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283499</v>
+        <v>283569</v>
       </c>
       <c r="R23" t="n">
-        <v>6527964</v>
+        <v>6527965</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3363,6 +3362,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3381,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315949</v>
+        <v>120315912</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3393,35 +3393,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283557</v>
+        <v>283535</v>
       </c>
       <c r="R24" t="n">
-        <v>6528002</v>
+        <v>6528012</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3467,13 +3467,17 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska hackringar/spår på flera träd</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3492,10 +3496,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315912</v>
+        <v>120315949</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3504,35 +3508,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3540,10 +3544,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283535</v>
+        <v>283557</v>
       </c>
       <c r="R25" t="n">
-        <v>6528012</v>
+        <v>6528002</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3578,17 +3582,13 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska hackringar/spår på flera träd</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3607,10 +3607,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315969</v>
+        <v>120315927</v>
       </c>
       <c r="B26" t="n">
-        <v>105588</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3619,31 +3619,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3651,10 +3659,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283509</v>
+        <v>283528</v>
       </c>
       <c r="R26" t="n">
-        <v>6528148</v>
+        <v>6528020</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3691,7 +3699,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Mängder med små askar</t>
+          <t>Ett par i sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3700,7 +3708,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3719,10 +3726,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315991</v>
+        <v>120315953</v>
       </c>
       <c r="B27" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3731,31 +3738,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3763,10 +3774,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283523</v>
+        <v>283450</v>
       </c>
       <c r="R27" t="n">
-        <v>6528173</v>
+        <v>6527951</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3801,18 +3812,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Mängder, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3831,10 +3836,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315929</v>
+        <v>120315991</v>
       </c>
       <c r="B28" t="n">
-        <v>57336</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3843,35 +3848,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3879,10 +3880,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283496</v>
+        <v>283523</v>
       </c>
       <c r="R28" t="n">
-        <v>6527938</v>
+        <v>6528173</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3917,12 +3918,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Mängder, kalkinslag i marken</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3941,10 +3948,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315942</v>
+        <v>120315972</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>100194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3953,32 +3960,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -3989,10 +3992,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>283569</v>
+        <v>283509</v>
       </c>
       <c r="R29" t="n">
-        <v>6527965</v>
+        <v>6528148</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4025,6 +4028,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4052,7 +4060,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315953</v>
+        <v>120315929</v>
       </c>
       <c r="B30" t="n">
         <v>57336</v>
@@ -4100,10 +4108,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283450</v>
+        <v>283496</v>
       </c>
       <c r="R30" t="n">
-        <v>6527951</v>
+        <v>6527938</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4162,10 +4170,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315947</v>
+        <v>120315940</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4174,35 +4182,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4210,10 +4218,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283569</v>
+        <v>283499</v>
       </c>
       <c r="R31" t="n">
-        <v>6527994</v>
+        <v>6527964</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4254,7 +4262,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4273,10 +4280,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315927</v>
+        <v>120315960</v>
       </c>
       <c r="B32" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4289,33 +4296,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4325,10 +4328,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283528</v>
+        <v>283506</v>
       </c>
       <c r="R32" t="n">
-        <v>6528020</v>
+        <v>6528143</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4361,11 +4364,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ett par i sitt permanenta revir</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4392,10 +4390,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315960</v>
+        <v>120315969</v>
       </c>
       <c r="B33" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4404,35 +4402,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4440,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283506</v>
+        <v>283509</v>
       </c>
       <c r="R33" t="n">
-        <v>6528143</v>
+        <v>6528148</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4478,12 +4472,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4502,10 +4502,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315972</v>
+        <v>120315982</v>
       </c>
       <c r="B34" t="n">
-        <v>100194</v>
+        <v>105588</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4514,25 +4514,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4546,10 +4546,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283509</v>
+        <v>283523</v>
       </c>
       <c r="R34" t="n">
-        <v>6528148</v>
+        <v>6528173</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4744,10 +4744,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120319417</v>
+        <v>120325558</v>
       </c>
       <c r="B36" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4756,35 +4756,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283722</v>
+        <v>283571</v>
       </c>
       <c r="R36" t="n">
-        <v>6528065</v>
+        <v>6528000</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4837,12 +4837,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4851,6 +4846,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5134,7 +5130,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120324201</v>
+        <v>120319417</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5182,10 +5178,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283761</v>
+        <v>283722</v>
       </c>
       <c r="R39" t="n">
-        <v>6528094</v>
+        <v>6528065</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5232,7 +5228,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5264,10 +5260,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120325558</v>
+        <v>120325002</v>
       </c>
       <c r="B40" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5276,35 +5272,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5312,10 +5312,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283571</v>
+        <v>283612</v>
       </c>
       <c r="R40" t="n">
-        <v>6528000</v>
+        <v>6528016</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5366,7 +5366,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5390,7 +5389,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120325002</v>
+        <v>120324201</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5430,11 +5429,7 @@
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283612</v>
+        <v>283761</v>
       </c>
       <c r="R41" t="n">
-        <v>6528016</v>
+        <v>6528094</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5477,7 +5472,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5487,7 +5482,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5630,10 +5630,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120512348</v>
+        <v>120513970</v>
       </c>
       <c r="B43" t="n">
-        <v>57336</v>
+        <v>57689</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5642,20 +5642,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5670,7 +5670,11 @@
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5678,13 +5682,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>283306</v>
+        <v>283036</v>
       </c>
       <c r="R43" t="n">
-        <v>6528054</v>
+        <v>6527980</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5708,27 +5712,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Hack i en döende tall</t>
+          <t>Endast hörde</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5755,10 +5759,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120513970</v>
+        <v>120514783</v>
       </c>
       <c r="B44" t="n">
-        <v>57689</v>
+        <v>57336</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5767,20 +5771,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5795,11 +5799,7 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5807,13 +5807,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>283036</v>
+        <v>283211</v>
       </c>
       <c r="R44" t="n">
-        <v>6527980</v>
+        <v>6528028</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Endast hörde</t>
+          <t>Hack på döende stor björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5884,7 +5884,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120514783</v>
+        <v>120512348</v>
       </c>
       <c r="B45" t="n">
         <v>57336</v>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>283211</v>
+        <v>283306</v>
       </c>
       <c r="R45" t="n">
-        <v>6528028</v>
+        <v>6528054</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5962,27 +5962,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack på döende stor björk</t>
+          <t>Hack i en döende tall</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -3159,10 +3159,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120315947</v>
+        <v>120315929</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3171,35 +3171,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>283569</v>
+        <v>283496</v>
       </c>
       <c r="R22" t="n">
-        <v>6527994</v>
+        <v>6527938</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3251,7 +3251,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3270,10 +3269,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120315942</v>
+        <v>120315927</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3282,35 +3281,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3318,10 +3321,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>283569</v>
+        <v>283528</v>
       </c>
       <c r="R23" t="n">
-        <v>6527965</v>
+        <v>6528020</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3356,13 +3359,17 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett par i sitt permanenta revir</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3381,10 +3388,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120315912</v>
+        <v>120315991</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>100194</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3393,35 +3400,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3429,10 +3432,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>283535</v>
+        <v>283523</v>
       </c>
       <c r="R24" t="n">
-        <v>6528012</v>
+        <v>6528173</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3469,7 +3472,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Färska hackringar/spår på flera träd</t>
+          <t>Mängder, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3478,6 +3481,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3496,10 +3500,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120315949</v>
+        <v>120315953</v>
       </c>
       <c r="B25" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3508,35 +3512,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3544,10 +3548,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>283557</v>
+        <v>283450</v>
       </c>
       <c r="R25" t="n">
-        <v>6528002</v>
+        <v>6527951</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3588,7 +3592,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3607,10 +3610,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120315927</v>
+        <v>120315969</v>
       </c>
       <c r="B26" t="n">
-        <v>57473</v>
+        <v>105588</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3619,39 +3622,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3659,10 +3654,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>283528</v>
+        <v>283509</v>
       </c>
       <c r="R26" t="n">
-        <v>6528020</v>
+        <v>6528148</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3699,7 +3694,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ett par i sitt permanenta revir</t>
+          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3708,6 +3703,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3726,10 +3722,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120315953</v>
+        <v>120315947</v>
       </c>
       <c r="B27" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3738,35 +3734,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3774,10 +3770,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>283450</v>
+        <v>283569</v>
       </c>
       <c r="R27" t="n">
-        <v>6527951</v>
+        <v>6527994</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3818,6 +3814,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3836,7 +3833,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120315991</v>
+        <v>120315972</v>
       </c>
       <c r="B28" t="n">
         <v>100194</v>
@@ -3880,10 +3877,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>283523</v>
+        <v>283509</v>
       </c>
       <c r="R28" t="n">
-        <v>6528173</v>
+        <v>6528148</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3920,7 +3917,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mängder, kalkinslag i marken</t>
+          <t>Mängder med blåsippor, kalkinslag i marken</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3948,10 +3945,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120315972</v>
+        <v>120315940</v>
       </c>
       <c r="B29" t="n">
-        <v>100194</v>
+        <v>57336</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3960,31 +3957,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3992,10 +3993,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>283509</v>
+        <v>283499</v>
       </c>
       <c r="R29" t="n">
-        <v>6528148</v>
+        <v>6527964</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4030,18 +4031,12 @@
           <t>2024-10-08</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mängder med blåsippor, kalkinslag i marken</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4060,10 +4055,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120315929</v>
+        <v>120315982</v>
       </c>
       <c r="B30" t="n">
-        <v>57336</v>
+        <v>105588</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4072,35 +4067,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4108,10 +4099,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>283496</v>
+        <v>283523</v>
       </c>
       <c r="R30" t="n">
-        <v>6527938</v>
+        <v>6528173</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4146,12 +4137,18 @@
           <t>2024-10-08</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Mängder med små askar</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4170,7 +4167,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315940</v>
+        <v>120315960</v>
       </c>
       <c r="B31" t="n">
         <v>57336</v>
@@ -4208,7 +4205,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4218,10 +4215,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283499</v>
+        <v>283506</v>
       </c>
       <c r="R31" t="n">
-        <v>6527964</v>
+        <v>6528143</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4280,10 +4277,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315960</v>
+        <v>120315942</v>
       </c>
       <c r="B32" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4292,35 +4289,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4328,10 +4325,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283506</v>
+        <v>283569</v>
       </c>
       <c r="R32" t="n">
-        <v>6528143</v>
+        <v>6527965</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4372,6 +4369,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4390,10 +4388,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120315969</v>
+        <v>120315912</v>
       </c>
       <c r="B33" t="n">
-        <v>105588</v>
+        <v>57320</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4402,31 +4400,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220785</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4434,10 +4436,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>283509</v>
+        <v>283535</v>
       </c>
       <c r="R33" t="n">
-        <v>6528148</v>
+        <v>6528012</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4474,7 +4476,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mängder med små askar</t>
+          <t>Färska hackringar/spår på flera träd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4483,7 +4485,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4502,10 +4503,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120315982</v>
+        <v>120315949</v>
       </c>
       <c r="B34" t="n">
-        <v>105588</v>
+        <v>97930</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4514,28 +4515,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -4546,10 +4551,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>283523</v>
+        <v>283557</v>
       </c>
       <c r="R34" t="n">
-        <v>6528173</v>
+        <v>6528002</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4582,11 +4587,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mängder med små askar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4614,7 +4614,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120325399</v>
+        <v>120319417</v>
       </c>
       <c r="B35" t="n">
         <v>57336</v>
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283598</v>
+        <v>283722</v>
       </c>
       <c r="R35" t="n">
-        <v>6527990</v>
+        <v>6528065</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Massor av hack en gammal nyss död gran</t>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5000,7 +5000,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120319318</v>
+        <v>120325002</v>
       </c>
       <c r="B38" t="n">
         <v>57336</v>
@@ -5040,18 +5040,22 @@
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283678</v>
+        <v>283612</v>
       </c>
       <c r="R38" t="n">
-        <v>6528180</v>
+        <v>6528016</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5083,7 +5087,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5093,12 +5097,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5130,7 +5129,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120319417</v>
+        <v>120324201</v>
       </c>
       <c r="B39" t="n">
         <v>57336</v>
@@ -5178,10 +5177,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283722</v>
+        <v>283761</v>
       </c>
       <c r="R39" t="n">
-        <v>6528065</v>
+        <v>6528094</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5228,7 +5227,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5260,7 +5259,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120325002</v>
+        <v>120319318</v>
       </c>
       <c r="B40" t="n">
         <v>57336</v>
@@ -5300,22 +5299,18 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283612</v>
+        <v>283678</v>
       </c>
       <c r="R40" t="n">
-        <v>6528016</v>
+        <v>6528180</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5347,7 +5342,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5357,7 +5352,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5389,7 +5389,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120324201</v>
+        <v>120325399</v>
       </c>
       <c r="B41" t="n">
         <v>57336</v>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283761</v>
+        <v>283598</v>
       </c>
       <c r="R41" t="n">
-        <v>6528094</v>
+        <v>6527990</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5519,7 +5519,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120512850</v>
+        <v>120512348</v>
       </c>
       <c r="B42" t="n">
         <v>57336</v>
@@ -5552,7 +5552,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -5563,10 +5567,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>283234</v>
+        <v>283306</v>
       </c>
       <c r="R42" t="n">
-        <v>6527956</v>
+        <v>6528054</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5596,14 +5600,24 @@
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-10-17</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Hack i död gran</t>
+          <t>Hack i en döende tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5884,10 +5898,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120512348</v>
+        <v>120514265</v>
       </c>
       <c r="B45" t="n">
-        <v>57336</v>
+        <v>56532</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5896,25 +5910,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5923,7 +5937,11 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5932,13 +5950,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>283306</v>
+        <v>283173</v>
       </c>
       <c r="R45" t="n">
-        <v>6528054</v>
+        <v>6528043</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5962,27 +5980,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack i en döende tall</t>
+          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6009,10 +6027,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120514265</v>
+        <v>120512850</v>
       </c>
       <c r="B46" t="n">
-        <v>56532</v>
+        <v>57336</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6021,38 +6039,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -6061,13 +6071,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>283173</v>
+        <v>283234</v>
       </c>
       <c r="R46" t="n">
-        <v>6528043</v>
+        <v>6527956</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6091,27 +6101,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
+          <t>Hack i död gran</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -4167,10 +4167,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120315960</v>
+        <v>120315942</v>
       </c>
       <c r="B31" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4179,35 +4179,35 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>283506</v>
+        <v>283569</v>
       </c>
       <c r="R31" t="n">
-        <v>6528143</v>
+        <v>6527965</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4259,6 +4259,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4278,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120315942</v>
+        <v>120315960</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4289,35 +4290,35 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4325,10 +4326,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>283569</v>
+        <v>283506</v>
       </c>
       <c r="R32" t="n">
-        <v>6527965</v>
+        <v>6528143</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4369,7 +4370,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -5522,11 +5522,11 @@
         <v>120514265</v>
       </c>
       <c r="B42" t="n">
-        <v>56560</v>
+        <v>56700</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,12 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100660</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>283111.6475530454</v>
+        <v>283112</v>
       </c>
       <c r="R10" t="n">
-        <v>6527998.356252665</v>
+        <v>6527998</v>
       </c>
       <c r="S10" t="n">
         <v>100</v>
@@ -1720,19 +1715,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1776,12 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97514</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>283111.6475530454</v>
+        <v>283112</v>
       </c>
       <c r="R11" t="n">
-        <v>6527998.356252665</v>
+        <v>6527998</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -1846,19 +1826,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1902,12 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,10 +1904,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R12" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S12" t="n">
         <v>100</v>
@@ -1972,19 +1937,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2028,12 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100753</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>283111.6475530454</v>
+        <v>283112</v>
       </c>
       <c r="R13" t="n">
-        <v>6527998.356252665</v>
+        <v>6527998</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -2098,19 +2048,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2154,12 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>106707</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2191,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R14" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S14" t="n">
         <v>100</v>
@@ -2224,19 +2159,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2280,12 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,10 +2237,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>283111.6475530454</v>
+        <v>283112</v>
       </c>
       <c r="R15" t="n">
-        <v>6527998.356252665</v>
+        <v>6527998</v>
       </c>
       <c r="S15" t="n">
         <v>100</v>
@@ -2350,19 +2270,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2406,12 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100753</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R16" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S16" t="n">
         <v>100</v>
@@ -2476,19 +2381,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2532,12 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2569,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R17" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S17" t="n">
         <v>100</v>
@@ -2602,19 +2492,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2658,12 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2695,10 +2570,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R18" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S18" t="n">
         <v>100</v>
@@ -2728,19 +2603,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2784,12 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,10 +2681,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>283111.6475530454</v>
+        <v>283112</v>
       </c>
       <c r="R19" t="n">
-        <v>6527998.356252665</v>
+        <v>6527998</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -2854,19 +2714,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2910,12 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>283232.5154296402</v>
+        <v>283233</v>
       </c>
       <c r="R20" t="n">
-        <v>6527929.835397779</v>
+        <v>6527930</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -2980,19 +2825,9 @@
           <t>1994-06-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>1994-06-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3036,12 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>96926</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99198</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3073,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>283451.6436885038</v>
+        <v>283452</v>
       </c>
       <c r="R21" t="n">
-        <v>6527982.370761711</v>
+        <v>6527982</v>
       </c>
       <c r="S21" t="n">
         <v>100</v>
@@ -3106,19 +2936,9 @@
           <t>1994-05-03</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>1994-05-03</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97514</v>
+        <v>97520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99198</v>
+        <v>99206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109134</v>
+        <v>109149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105521</v>
+        <v>105533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100753</v>
+        <v>100761</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102800</v>
+        <v>102811</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110300</v>
+        <v>110315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105521</v>
+        <v>105533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99198</v>
+        <v>99206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97520</v>
+        <v>97526</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99206</v>
+        <v>99212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109149</v>
+        <v>109158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105533</v>
+        <v>105542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100761</v>
+        <v>100768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102811</v>
+        <v>102819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110315</v>
+        <v>110324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105533</v>
+        <v>105542</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99206</v>
+        <v>99212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97526</v>
+        <v>97528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99212</v>
+        <v>99215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109158</v>
+        <v>109171</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105542</v>
+        <v>105554</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100768</v>
+        <v>100773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102819</v>
+        <v>102829</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110324</v>
+        <v>110337</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105542</v>
+        <v>105554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99212</v>
+        <v>99215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109171</v>
+        <v>109180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102829</v>
+        <v>102835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110337</v>
+        <v>110346</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105554</v>
+        <v>105563</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97528</v>
+        <v>97529</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109180</v>
+        <v>109185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102835</v>
+        <v>102836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110346</v>
+        <v>110351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105563</v>
+        <v>105566</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97529</v>
+        <v>97556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109185</v>
+        <v>109213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102836</v>
+        <v>102863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110351</v>
+        <v>110379</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105566</v>
+        <v>105594</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97556</v>
+        <v>97562</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109213</v>
+        <v>109219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102863</v>
+        <v>102869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100713</v>
+        <v>100719</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110379</v>
+        <v>110385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105594</v>
+        <v>105600</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97562</v>
+        <v>97569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109219</v>
+        <v>109226</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102869</v>
+        <v>102876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100719</v>
+        <v>100726</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110385</v>
+        <v>110392</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105600</v>
+        <v>105607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97569</v>
+        <v>97573</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109226</v>
+        <v>109230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102876</v>
+        <v>102880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110392</v>
+        <v>110396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105607</v>
+        <v>105611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97573</v>
+        <v>97580</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109230</v>
+        <v>109238</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102880</v>
+        <v>102887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110396</v>
+        <v>110404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105611</v>
+        <v>105618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1650,7 +1650,7 @@
         <v>90929862</v>
       </c>
       <c r="B10" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>90929876</v>
       </c>
       <c r="B11" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>90930000</v>
       </c>
       <c r="B12" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>90929868</v>
       </c>
       <c r="B13" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>90929957</v>
       </c>
       <c r="B14" t="n">
-        <v>109241</v>
+        <v>109246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>90929865</v>
       </c>
       <c r="B15" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>90929979</v>
       </c>
       <c r="B16" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
         <v>90929985</v>
       </c>
       <c r="B17" t="n">
-        <v>102890</v>
+        <v>102895</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>90929976</v>
       </c>
       <c r="B18" t="n">
-        <v>100740</v>
+        <v>100745</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>90929863</v>
       </c>
       <c r="B19" t="n">
-        <v>110407</v>
+        <v>110412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>90929977</v>
       </c>
       <c r="B20" t="n">
-        <v>105621</v>
+        <v>105626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>91411612</v>
       </c>
       <c r="B21" t="n">
-        <v>99275</v>
+        <v>99280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4434,10 +4434,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120325465</v>
+        <v>120319530</v>
       </c>
       <c r="B35" t="n">
-        <v>57349</v>
+        <v>88442</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4446,35 +4446,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>4394</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Honungsvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hygrocybe reidii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4482,10 +4481,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>283549</v>
+        <v>283704</v>
       </c>
       <c r="R35" t="n">
-        <v>6528013</v>
+        <v>6527984</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4517,7 +4516,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4527,12 +4526,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Kanske flera många hack på en död tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,6 +4535,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4564,7 +4559,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120324201</v>
+        <v>120325465</v>
       </c>
       <c r="B36" t="n">
         <v>57349</v>
@@ -4612,10 +4607,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>283761</v>
+        <v>283549</v>
       </c>
       <c r="R36" t="n">
-        <v>6528094</v>
+        <v>6528013</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4647,7 +4642,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4657,12 +4652,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd gammal gran</t>
+          <t>Kanske flera många hack på en död tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4694,7 +4689,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120319417</v>
+        <v>120324201</v>
       </c>
       <c r="B37" t="n">
         <v>57349</v>
@@ -4742,10 +4737,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>283722</v>
+        <v>283761</v>
       </c>
       <c r="R37" t="n">
-        <v>6528065</v>
+        <v>6528094</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4792,7 +4787,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Hack i en halvdöd tall</t>
+          <t>Hack i en halvdöd gammal gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4824,7 +4819,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120319318</v>
+        <v>120319417</v>
       </c>
       <c r="B38" t="n">
         <v>57349</v>
@@ -4868,14 +4863,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Skee, Boh</t>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>283678</v>
+        <v>283722</v>
       </c>
       <c r="R38" t="n">
-        <v>6528180</v>
+        <v>6528065</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4907,7 +4902,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4917,12 +4912,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Hackspår i en gammal halvdöd tall</t>
+          <t>Hack i en halvdöd tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4954,7 +4949,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120325002</v>
+        <v>120319318</v>
       </c>
       <c r="B39" t="n">
         <v>57349</v>
@@ -4994,22 +4989,18 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
+          <t>Stora Holma, Överby, Skee, Boh</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>283612</v>
+        <v>283678</v>
       </c>
       <c r="R39" t="n">
-        <v>6528016</v>
+        <v>6528180</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -5041,7 +5032,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5051,7 +5042,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Hackspår i en gammal halvdöd tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5083,7 +5079,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120325399</v>
+        <v>120325002</v>
       </c>
       <c r="B40" t="n">
         <v>57349</v>
@@ -5123,7 +5119,11 @@
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5131,10 +5131,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>283598</v>
+        <v>283612</v>
       </c>
       <c r="R40" t="n">
-        <v>6527990</v>
+        <v>6528016</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5177,11 +5177,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5213,10 +5208,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120325558</v>
+        <v>120325399</v>
       </c>
       <c r="B41" t="n">
-        <v>98005</v>
+        <v>57349</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5225,35 +5220,35 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>283571</v>
+        <v>283598</v>
       </c>
       <c r="R41" t="n">
-        <v>6528000</v>
+        <v>6527990</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5296,7 +5291,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5306,7 +5301,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Massor av hack en gammal nyss död gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5315,7 +5315,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5339,51 +5338,47 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120514265</v>
+        <v>120325558</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>98005</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5391,13 +5386,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>283173</v>
+        <v>283571</v>
       </c>
       <c r="R42" t="n">
-        <v>6528043</v>
+        <v>6528000</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5421,27 +5416,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5450,8 +5440,14 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5468,10 +5464,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120513970</v>
+        <v>120319484</v>
       </c>
       <c r="B43" t="n">
-        <v>57717</v>
+        <v>91946</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5480,39 +5476,34 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>5966</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5520,13 +5511,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>283036</v>
+        <v>283711</v>
       </c>
       <c r="R43" t="n">
-        <v>6527980</v>
+        <v>6527978</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5550,27 +5541,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Endast hörde</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5579,8 +5565,14 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5597,7 +5589,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120514783</v>
+        <v>120512584</v>
       </c>
       <c r="B44" t="n">
         <v>57364</v>
@@ -5645,10 +5637,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>283211</v>
+        <v>283264</v>
       </c>
       <c r="R44" t="n">
-        <v>6528028</v>
+        <v>6528002</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5675,27 +5667,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Hack på döende stor björk</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5722,37 +5709,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120512348</v>
+        <v>120514265</v>
       </c>
       <c r="B45" t="n">
-        <v>57364</v>
+        <v>56722</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5761,7 +5748,11 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5770,13 +5761,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>283306</v>
+        <v>283173</v>
       </c>
       <c r="R45" t="n">
-        <v>6528054</v>
+        <v>6528043</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5800,27 +5791,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Hack i en döende tall</t>
+          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5847,10 +5838,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120512850</v>
+        <v>120513970</v>
       </c>
       <c r="B46" t="n">
-        <v>57364</v>
+        <v>57717</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5859,20 +5850,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5880,10 +5871,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5891,13 +5890,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>283234</v>
+        <v>283036</v>
       </c>
       <c r="R46" t="n">
-        <v>6527956</v>
+        <v>6527980</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5921,17 +5920,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Hack i död gran</t>
+          <t>Endast hörde</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5955,6 +5964,492 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120512644</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57364</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>283229</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6527964</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Hack i en död gran som tappart bar i basen</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120514783</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57364</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>283211</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6528028</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hack på döende stor björk</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120512348</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57364</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>283306</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6528054</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Hack i en döende tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120512850</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57364</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stora Holma, Överby, Strömstad, Boh</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>283234</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6527956</v>
+      </c>
+      <c r="S50" t="n">
+        <v>1</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Strömstad</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Skee</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Svenson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5464,46 +5464,51 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120319484</v>
+        <v>120514265</v>
       </c>
       <c r="B43" t="n">
-        <v>91946</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5511,13 +5516,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>283711</v>
+        <v>283173</v>
       </c>
       <c r="R43" t="n">
-        <v>6527978</v>
+        <v>6528043</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5541,22 +5546,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5565,14 +5575,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5589,10 +5593,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120512584</v>
+        <v>120513970</v>
       </c>
       <c r="B44" t="n">
-        <v>57364</v>
+        <v>57717</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5601,20 +5605,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5629,7 +5633,11 @@
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5637,13 +5645,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>283264</v>
+        <v>283036</v>
       </c>
       <c r="R44" t="n">
-        <v>6528002</v>
+        <v>6527980</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5667,22 +5675,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Endast hörde</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5709,37 +5722,37 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120514265</v>
+        <v>120512644</v>
       </c>
       <c r="B45" t="n">
-        <v>56722</v>
+        <v>57364</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5748,11 +5761,7 @@
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
@@ -5761,13 +5770,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>283173</v>
+        <v>283229</v>
       </c>
       <c r="R45" t="n">
-        <v>6528043</v>
+        <v>6527964</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5791,27 +5800,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flög framför mig snabbt mellan granar. Möjligen hade jag skrämt henne.</t>
+          <t>Hack i en död gran som tappart bar i basen</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5838,10 +5847,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120513970</v>
+        <v>120514783</v>
       </c>
       <c r="B46" t="n">
-        <v>57717</v>
+        <v>57364</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5850,20 +5859,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5878,11 +5887,7 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5890,13 +5895,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>283036</v>
+        <v>283211</v>
       </c>
       <c r="R46" t="n">
-        <v>6527980</v>
+        <v>6528028</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5940,7 +5945,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Endast hörde</t>
+          <t>Hack på döende stor björk</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5967,7 +5972,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120512644</v>
+        <v>120512348</v>
       </c>
       <c r="B47" t="n">
         <v>57364</v>
@@ -6015,10 +6020,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>283229</v>
+        <v>283306</v>
       </c>
       <c r="R47" t="n">
-        <v>6527964</v>
+        <v>6528054</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6050,7 +6055,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6060,12 +6065,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack i en död gran som tappart bar i basen</t>
+          <t>Hack i en döende tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6092,7 +6097,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120514783</v>
+        <v>120512850</v>
       </c>
       <c r="B48" t="n">
         <v>57364</v>
@@ -6125,11 +6130,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -6140,10 +6141,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>283211</v>
+        <v>283234</v>
       </c>
       <c r="R48" t="n">
-        <v>6528028</v>
+        <v>6527956</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6170,27 +6171,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Hack på döende stor björk</t>
+          <t>Hack i död gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6214,242 +6205,6 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>120512348</v>
-      </c>
-      <c r="B49" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>283306</v>
-      </c>
-      <c r="R49" t="n">
-        <v>6528054</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Strömstad</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Skee</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Hack i en döende tall</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Erland Svenson</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Erland Svenson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>120512850</v>
-      </c>
-      <c r="B50" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Stora Holma, Överby, Strömstad, Boh</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>283234</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6527956</v>
-      </c>
-      <c r="S50" t="n">
-        <v>1</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Strömstad</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Skee</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2024-10-17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hack i död gran</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Erland Svenson</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Erland Svenson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,12 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>283153.0189479042</v>
+        <v>283153</v>
       </c>
       <c r="R7" t="n">
-        <v>6528077.987841389</v>
+        <v>6528078</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,19 +1342,9 @@
           <t>1994-06-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1994-06-23</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110488</v>
+        <v>110491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110491</v>
+        <v>110520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110520</v>
+        <v>110532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110532</v>
+        <v>110533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110533</v>
+        <v>110538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110538</v>
+        <v>110542</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110542</v>
+        <v>110544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 34077-2023 artfynd.xlsx
+++ b/artfynd/A 34077-2023 artfynd.xlsx
@@ -1272,7 +1272,7 @@
         <v>5296077</v>
       </c>
       <c r="B7" t="n">
-        <v>110544</v>
+        <v>110579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
